--- a/artfynd/A 31073-2024 artfynd.xlsx
+++ b/artfynd/A 31073-2024 artfynd.xlsx
@@ -1989,11 +1989,11 @@
         <v>119205432</v>
       </c>
       <c r="B14" t="n">
-        <v>91840</v>
+        <v>92006</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Rackarbergen (Rackarbergen), Upl</t>
+          <t>Rackarbergen, Rackarbergen, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">

--- a/artfynd/A 31073-2024 artfynd.xlsx
+++ b/artfynd/A 31073-2024 artfynd.xlsx
@@ -1989,7 +1989,7 @@
         <v>119205432</v>
       </c>
       <c r="B14" t="n">
-        <v>92006</v>
+        <v>92020</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 31073-2024 artfynd.xlsx
+++ b/artfynd/A 31073-2024 artfynd.xlsx
@@ -1989,7 +1989,7 @@
         <v>119205432</v>
       </c>
       <c r="B14" t="n">
-        <v>92020</v>
+        <v>92022</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 31073-2024 artfynd.xlsx
+++ b/artfynd/A 31073-2024 artfynd.xlsx
@@ -1989,7 +1989,7 @@
         <v>119205432</v>
       </c>
       <c r="B14" t="n">
-        <v>92022</v>
+        <v>92023</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 31073-2024 artfynd.xlsx
+++ b/artfynd/A 31073-2024 artfynd.xlsx
@@ -1989,7 +1989,7 @@
         <v>119205432</v>
       </c>
       <c r="B14" t="n">
-        <v>92023</v>
+        <v>92032</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
